--- a/output/pdf_financials_xlsx/PBM.xlsx
+++ b/output/pdf_financials_xlsx/PBM.xlsx
@@ -6287,22 +6287,22 @@
         <v>2.943481</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.943481</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>8.833406</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.946444</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.946444</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.203148</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.203148</v>
       </c>
       <c r="P92" s="3" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         <v>-0.003117</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.046851</v>
+        <v>-0.054122</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>-0.100337</v>
@@ -13864,7 +13864,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14604,7 +14608,11 @@
           <t>Share-based payments reserve 12</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15120,7 +15128,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -17150,7 +17162,11 @@
           <t>Share-based payments reserve 2,943,481</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18974,7 +18990,11 @@
           <t>Share-based payments reserve 2,946,444</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -19498,7 +19518,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -33032,7 +33056,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PBM.xlsx
+++ b/output/pdf_financials_xlsx/PBM.xlsx
@@ -1069,28 +1069,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.10897</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.036292</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003301</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004494</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000162</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>4.8e-05</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000171</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000625</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.002204</v>
       </c>
     </row>
     <row r="13">
@@ -2072,28 +2072,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.032781</v>
+        <v>-1.141751</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.667179</v>
+        <v>-0.703471</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.217947</v>
+        <v>-1.221248</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.815553</v>
+        <v>-0.820047</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.159393</v>
+        <v>-1.159555</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.57238</v>
+        <v>-1.5725</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.263867</v>
+        <v>-0.263966</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.61532</v>
+        <v>-0.615416</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.543152</v>
@@ -2114,16 +2114,16 @@
         <v>-0.251966</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.029962</v>
+        <v>-0.03001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.052254</v>
+        <v>-1.052425</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.146582</v>
+        <v>-0.147207</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.142605</v>
+        <v>-0.144809</v>
       </c>
     </row>
     <row r="28">
@@ -2194,28 +2194,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.031377</v>
+        <v>-1.140347</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.661042</v>
+        <v>-0.697334</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.207599</v>
+        <v>-1.2109</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.8073</v>
+        <v>-0.811794</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.150382</v>
+        <v>-1.150544</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.568214</v>
+        <v>-1.568334</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.261984</v>
+        <v>-0.262083</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.613812</v>
+        <v>-0.613908</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.541947</v>
@@ -2236,16 +2236,16 @@
         <v>-0.251571</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.029646</v>
+        <v>-0.029694</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.052002</v>
+        <v>-1.052173</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.14638</v>
+        <v>-0.147005</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.142455</v>
+        <v>-0.144659</v>
       </c>
     </row>
     <row r="30">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-2046.04</v>
+        <v>-2046.36</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>724.7993901460439</v>
@@ -2535,34 +2535,34 @@
         <v>0.002523</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000941</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003684</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.061201</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.339561</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.124446</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.039267</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.006063</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.003585</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.049859</v>
       </c>
     </row>
     <row r="35">
@@ -2661,34 +2661,34 @@
         <v>0.002523</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000941</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003684</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.061201</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.339561</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.124446</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.039267</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.006063</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.003585</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.049859</v>
       </c>
     </row>
     <row r="37">
@@ -3417,34 +3417,34 @@
         <v>0.002507</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.001205</v>
+        <v>0.000264</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.007594</v>
+        <v>0.00391</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.061201</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000526</v>
+        <v>0.000274</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.339656</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.129615</v>
+        <v>0.005169</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.063627</v>
+        <v>0.02436</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.006506</v>
+        <v>0.000443</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.039385</v>
+        <v>0.0358</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.049859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9276,7 +9276,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -9672,7 +9676,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -11582,7 +11590,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12622,7 +12634,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -15866,7 +15882,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -16406,7 +16422,11 @@
           <t>Reclamation deposits 12,000</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -17698,7 +17718,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -18128,7 +18148,11 @@
           <t>Reclamation deposits 17,000</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -33268,7 +33292,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -34954,7 +34982,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -48074,7 +48106,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -48182,7 +48214,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -59840,7 +59872,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -61332,7 +61364,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -62504,7 +62536,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E515" s="5" t="n">

--- a/output/pdf_financials_xlsx/PBM.xlsx
+++ b/output/pdf_financials_xlsx/PBM.xlsx
@@ -7450,13 +7450,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.007823999999999999</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0326</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -42172,7 +42172,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PBM.xlsx
+++ b/output/pdf_financials_xlsx/PBM.xlsx
@@ -1316,7 +1316,7 @@
         <v>-1.032781</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.667179</v>
+        <v>-0.225179</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.217947</v>
@@ -1377,13 +1377,13 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.442</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.109783</v>
+        <v>-0.109783</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2075,7 +2075,7 @@
         <v>-1.141751</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.703471</v>
+        <v>-0.261471</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.221248</v>
@@ -2197,7 +2197,7 @@
         <v>-1.140347</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.697334</v>
+        <v>-0.255334</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.2109</v>
@@ -2351,7 +2351,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-196.2882862078613</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4649,37 +4649,37 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.015271</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.043722</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.035963</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.049472</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.022007</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.033642</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.022722</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.031902</v>
       </c>
     </row>
     <row r="68">
@@ -4715,34 +4715,34 @@
         <v>0.236046</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.192972</v>
+        <v>0.205472</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.209758</v>
+        <v>0.224758</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.316466</v>
+        <v>0.360188</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.167476</v>
+        <v>0.203439</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.165415</v>
+        <v>0.214887</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.148017</v>
+        <v>0.170024</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.210463</v>
+        <v>0.230463</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.254649</v>
+        <v>0.288291</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.283456</v>
+        <v>0.306178</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.366949</v>
+        <v>0.398851</v>
       </c>
     </row>
     <row r="69">
@@ -5165,16 +5165,16 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.592029</v>
+        <v>0.5560659999999999</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.784017</v>
+        <v>0.734545</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.891966</v>
+        <v>0.869959</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.555023</v>
+        <v>0.535023</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0.002243</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001909</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>-0.007789</v>
@@ -7102,7 +7102,7 @@
         <v>0.001498</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.022963</v>
+        <v>0.021054</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.02849</v>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06597799999999999</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024286</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.155835</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.549806</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06597799999999999</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024286</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.727092</v>
+        <v>-0.7930700000000001</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -35196,7 +35196,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -42902,7 +42906,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -43322,7 +43330,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -44572,7 +44584,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E342" s="5" t="n">
         <v>-0.06597799999999999</v>
       </c>
@@ -64204,7 +64220,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -65880,7 +65900,11 @@
           <t>Future income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -68198,7 +68222,11 @@
           <t>Future income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>-</t>
